--- a/UserDetails.xlsx
+++ b/UserDetails.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{95F3F662-50CC-444A-91DF-5199A35F61C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{E8521EE3-EA53-4D58-9A80-9643BE2B17EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
